--- a/artfynd/A 14482-2023 artfynd.xlsx
+++ b/artfynd/A 14482-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14482-2023 artfynd.xlsx
+++ b/artfynd/A 14482-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>61569670</v>
       </c>
       <c r="B2" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792021.0570877558</v>
+        <v>792021</v>
       </c>
       <c r="R2" t="n">
-        <v>7431194.924423117</v>
+        <v>7431195</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,19 +749,9 @@
           <t>2016-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,42 +779,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61569671</v>
+        <v>61569672</v>
       </c>
       <c r="B3" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792021.0570877558</v>
+        <v>792021</v>
       </c>
       <c r="R3" t="n">
-        <v>7431194.924423117</v>
+        <v>7431195</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +853,9 @@
           <t>2016-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,42 +883,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61569672</v>
+        <v>61569671</v>
       </c>
       <c r="B4" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792021.0570877558</v>
+        <v>792021</v>
       </c>
       <c r="R4" t="n">
-        <v>7431194.924423117</v>
+        <v>7431195</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -992,19 +957,9 @@
           <t>2016-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 14482-2023 artfynd.xlsx
+++ b/artfynd/A 14482-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569670</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61569671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>